--- a/FSW characteristics.xlsx
+++ b/FSW characteristics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lovel\Documents\GitHub\hiv-modelling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FCB07B-E6FE-4811-A9DA-41E8818C023C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D55BF88-A1F2-4893-A3E1-1947E0FE8FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="1" xr2:uid="{F092BB82-033B-4CB9-BD3B-04613BC11C15}"/>
   </bookViews>
